--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,8 +992,18 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489130</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064788</v>
+        <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svedjebodarna, Jmt</t>
+          <t>Svedbodarna sv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445736</v>
+        <v>445784</v>
       </c>
       <c r="R3" t="n">
-        <v>7037107</v>
+        <v>7037162</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +888,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131064788</t>
+          <t>https://artportalen.se/Sighting/135917694</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91489130</v>
+        <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>98137</v>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222741</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Svedbodarna sv, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445795</v>
+        <v>445754</v>
       </c>
       <c r="R4" t="n">
-        <v>7037111</v>
+        <v>7037225</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,31 +985,2032 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Friskt högörtsparti</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917699</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135917698</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>445750</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7037205</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917698</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135917704</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>445714</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7037317</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917704</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135917690</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>445815</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037098</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917690</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131064788</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svedjebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>445736</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7037107</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064788</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135917678</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99614</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>445836</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7037106</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917678</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135917681</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99614</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>445830</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037105</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917681</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135917685</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99614</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>445822</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037070</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917685</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135917691</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99614</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445814</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037105</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917691</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135917674</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110014</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>445799</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037269</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917674</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135917686</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110014</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>445821</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7037069</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917686</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135917696</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>445772</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037196</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917696</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135917701</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>445752</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7037256</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917701</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135917677</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>445846</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037110</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917677</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135917680</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>445827</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7037105</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917680</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135917688</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>445808</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7037060</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917688</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135917693</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>445797</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7037149</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917693</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>91489130</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>445795</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7037111</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Friskt högörtsparti</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91489130</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135917683</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98292</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svedbodarna sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>445831</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7037074</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917683</t>
         </is>
       </c>
     </row>
@@ -1003,6 +3019,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98292</v>
+        <v>98309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110039</v>
+        <v>110040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110039</v>
+        <v>110040</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98310</v>
+        <v>98311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98311</v>
+        <v>98312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98312</v>
+        <v>98318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98318</v>
+        <v>98319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98319</v>
+        <v>98330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98330</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>98344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98344</v>
+        <v>98357</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2026 artfynd.xlsx
+++ b/artfynd/A 30590-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917694</v>
       </c>
       <c r="B3" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135917699</v>
       </c>
       <c r="B4" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917698</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135917704</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917690</v>
       </c>
       <c r="B7" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135917678</v>
       </c>
       <c r="B9" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135917681</v>
       </c>
       <c r="B10" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135917685</v>
       </c>
       <c r="B11" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135917691</v>
       </c>
       <c r="B12" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>135917674</v>
       </c>
       <c r="B13" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135917686</v>
       </c>
       <c r="B14" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135917696</v>
       </c>
       <c r="B15" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135917701</v>
       </c>
       <c r="B16" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135917677</v>
       </c>
       <c r="B17" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135917680</v>
       </c>
       <c r="B18" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135917688</v>
       </c>
       <c r="B19" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135917693</v>
       </c>
       <c r="B20" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135917683</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>98358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
